--- a/results/DR_results/01_pollution_assessment/MaxRel_Focus/tables/varpart_summary.xlsx
+++ b/results/DR_results/01_pollution_assessment/MaxRel_Focus/tables/varpart_summary.xlsx
@@ -470,25 +470,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.1643584187352317</v>
+        <v>0.2064474062421109</v>
       </c>
       <c r="C2" t="n">
-        <v>0.124871337044808</v>
+        <v>0.1354023135175015</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3306648689662953</v>
+        <v>0.3912618967862433</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2057935319214873</v>
+        <v>0.2558595832687418</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.04143511318625559</v>
+        <v>-0.04941217702663092</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1663064502310636</v>
+        <v>0.1848144905441325</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6693351310337047</v>
+        <v>0.6087381032137567</v>
       </c>
     </row>
   </sheetData>
